--- a/data/H131_20260622_18.xlsx
+++ b/data/H131_20260622_18.xlsx
@@ -593,7 +593,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>882.0</v>
+        <v>892.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -605,13 +605,13 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>882.0</v>
+        <v>892.0</v>
       </c>
       <c r="O4" s="2">
-        <v>518.0</v>
+        <v>525.0</v>
       </c>
       <c r="P4" s="2">
-        <v>364.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0</v>
@@ -806,7 +806,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" s="2">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="K7" s="2">
         <v>1.0</v>
@@ -818,10 +818,10 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="O7" s="2">
-        <v>272.0</v>
+        <v>274.0</v>
       </c>
       <c r="P7" s="2">
         <v>196.0</v>
@@ -836,7 +836,7 @@
         <v>13.0</v>
       </c>
       <c r="T7" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U7" s="2">
         <v>4.0</v>
@@ -845,7 +845,7 @@
         <v>0.0</v>
       </c>
       <c r="W7" s="2">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="8">
@@ -2013,7 +2013,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>1214.0</v>
+        <v>1215.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2025,10 +2025,10 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>1214.0</v>
+        <v>1215.0</v>
       </c>
       <c r="O24" s="2">
-        <v>740.0</v>
+        <v>741.0</v>
       </c>
       <c r="P24" s="2">
         <v>452.0</v>
@@ -2581,7 +2581,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" s="2">
-        <v>994.0</v>
+        <v>1021.0</v>
       </c>
       <c r="K32" s="2">
         <v>1.0</v>
@@ -2593,16 +2593,16 @@
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <v>994.0</v>
+        <v>1021.0</v>
       </c>
       <c r="O32" s="2">
-        <v>492.0</v>
+        <v>503.0</v>
       </c>
       <c r="P32" s="2">
-        <v>470.0</v>
+        <v>484.0</v>
       </c>
       <c r="Q32" s="2">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="R32" s="2">
         <v>15.0</v>
@@ -2614,13 +2614,13 @@
         <v>8.0</v>
       </c>
       <c r="U32" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="V32" s="2">
         <v>0.0</v>
       </c>
       <c r="W32" s="2">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -3362,7 +3362,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" s="2">
-        <v>965.0</v>
+        <v>969.0</v>
       </c>
       <c r="K43" s="2">
         <v>1.0</v>
@@ -3374,16 +3374,16 @@
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <v>965.0</v>
+        <v>969.0</v>
       </c>
       <c r="O43" s="2">
-        <v>501.0</v>
+        <v>504.0</v>
       </c>
       <c r="P43" s="2">
         <v>452.0</v>
       </c>
       <c r="Q43" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R43" s="2">
         <v>30.0</v>
@@ -3717,7 +3717,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>1038.0</v>
+        <v>1040.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3729,10 +3729,10 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>1038.0</v>
+        <v>1040.0</v>
       </c>
       <c r="O48" s="2">
-        <v>623.0</v>
+        <v>625.0</v>
       </c>
       <c r="P48" s="2">
         <v>410.0</v>
@@ -3803,13 +3803,13 @@
         <v>1354.0</v>
       </c>
       <c r="O49" s="2">
-        <v>777.0</v>
+        <v>778.0</v>
       </c>
       <c r="P49" s="2">
         <v>538.0</v>
       </c>
       <c r="Q49" s="2">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="R49" s="2">
         <v>68.0</v>
@@ -5847,7 +5847,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>1093.0</v>
+        <v>1110.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5859,13 +5859,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>1093.0</v>
+        <v>1110.0</v>
       </c>
       <c r="O78" s="2">
-        <v>495.0</v>
+        <v>510.0</v>
       </c>
       <c r="P78" s="2">
-        <v>598.0</v>
+        <v>600.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -5877,7 +5877,7 @@
         <v>56.0</v>
       </c>
       <c r="T78" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="U78" s="2">
         <v>9.0</v>
@@ -5886,7 +5886,7 @@
         <v>1.0</v>
       </c>
       <c r="W78" s="2">
-        <v>130.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
@@ -6155,13 +6155,13 @@
         <v>9.0</v>
       </c>
       <c r="R82" s="2">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="S82" s="2">
         <v>57.0</v>
       </c>
       <c r="T82" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="U82" s="2">
         <v>0.0</v>
@@ -6170,7 +6170,7 @@
         <v>0.0</v>
       </c>
       <c r="W82" s="2">
-        <v>128.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
@@ -6202,7 +6202,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" s="2">
-        <v>1042.0</v>
+        <v>1053.0</v>
       </c>
       <c r="K83" s="2">
         <v>1.0</v>
@@ -6214,22 +6214,22 @@
         <v>0.0</v>
       </c>
       <c r="N83" s="2">
-        <v>1042.0</v>
+        <v>1053.0</v>
       </c>
       <c r="O83" s="2">
-        <v>569.0</v>
+        <v>574.0</v>
       </c>
       <c r="P83" s="2">
-        <v>452.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q83" s="2">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="R83" s="2">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="S83" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="T83" s="2">
         <v>8.0</v>
@@ -6241,7 +6241,7 @@
         <v>0.0</v>
       </c>
       <c r="W83" s="2">
-        <v>69.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -7267,7 +7267,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>1366.0</v>
+        <v>1376.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7279,22 +7279,22 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>1366.0</v>
+        <v>1376.0</v>
       </c>
       <c r="O98" s="2">
-        <v>731.0</v>
+        <v>736.0</v>
       </c>
       <c r="P98" s="2">
         <v>623.0</v>
       </c>
       <c r="Q98" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="R98" s="2">
         <v>27.0</v>
       </c>
       <c r="S98" s="2">
-        <v>22.0</v>
+        <v>29.0</v>
       </c>
       <c r="T98" s="2">
         <v>7.0</v>
@@ -7306,7 +7306,7 @@
         <v>1.0</v>
       </c>
       <c r="W98" s="2">
-        <v>57.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -8048,7 +8048,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" s="2">
-        <v>770.0</v>
+        <v>771.0</v>
       </c>
       <c r="K109" s="2">
         <v>1.0</v>
@@ -8060,10 +8060,10 @@
         <v>0.0</v>
       </c>
       <c r="N109" s="2">
-        <v>770.0</v>
+        <v>771.0</v>
       </c>
       <c r="O109" s="2">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="P109" s="2">
         <v>341.0</v>
@@ -8403,7 +8403,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>863.0</v>
+        <v>866.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8415,10 +8415,10 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>863.0</v>
+        <v>866.0</v>
       </c>
       <c r="O114" s="2">
-        <v>522.0</v>
+        <v>525.0</v>
       </c>
       <c r="P114" s="2">
         <v>340.0</v>
@@ -8430,7 +8430,7 @@
         <v>29.0</v>
       </c>
       <c r="S114" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="T114" s="2">
         <v>0.0</v>
@@ -8442,7 +8442,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8687,7 +8687,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>1136.0</v>
+        <v>1152.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8699,19 +8699,19 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>1136.0</v>
+        <v>1152.0</v>
       </c>
       <c r="O118" s="2">
-        <v>642.0</v>
+        <v>654.0</v>
       </c>
       <c r="P118" s="2">
-        <v>488.0</v>
+        <v>492.0</v>
       </c>
       <c r="Q118" s="2">
         <v>6.0</v>
       </c>
       <c r="R118" s="2">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="S118" s="2">
         <v>24.0</v>
@@ -8726,7 +8726,7 @@
         <v>7.0</v>
       </c>
       <c r="W118" s="2">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
@@ -8829,7 +8829,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>866.0</v>
+        <v>877.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8841,25 +8841,25 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>866.0</v>
+        <v>877.0</v>
       </c>
       <c r="O120" s="2">
-        <v>478.0</v>
+        <v>484.0</v>
       </c>
       <c r="P120" s="2">
-        <v>354.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q120" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="R120" s="2">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="S120" s="2">
         <v>6.0</v>
       </c>
       <c r="T120" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U120" s="2">
         <v>3.0</v>
@@ -8868,7 +8868,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" s="2">
-        <v>56.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -8900,7 +8900,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>1258.0</v>
+        <v>1300.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8912,22 +8912,22 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>1258.0</v>
+        <v>1300.0</v>
       </c>
       <c r="O121" s="2">
-        <v>802.0</v>
+        <v>819.0</v>
       </c>
       <c r="P121" s="2">
-        <v>434.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q121" s="2">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="R121" s="2">
-        <v>27.0</v>
+        <v>38.0</v>
       </c>
       <c r="S121" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="T121" s="2">
         <v>0.0</v>
@@ -8939,7 +8939,7 @@
         <v>0.0</v>
       </c>
       <c r="W121" s="2">
-        <v>36.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -8971,7 +8971,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>778.0</v>
+        <v>783.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8983,13 +8983,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>774.0</v>
+        <v>779.0</v>
       </c>
       <c r="O122" s="2">
-        <v>428.0</v>
+        <v>430.0</v>
       </c>
       <c r="P122" s="2">
-        <v>335.0</v>
+        <v>338.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9696,13 +9696,13 @@
         <v>1359.0</v>
       </c>
       <c r="O132" s="2">
-        <v>768.0</v>
+        <v>769.0</v>
       </c>
       <c r="P132" s="2">
         <v>567.0</v>
       </c>
       <c r="Q132" s="2">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="R132" s="2">
         <v>27.0</v>
@@ -10036,7 +10036,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>1001.0</v>
+        <v>1002.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10048,10 +10048,10 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>1001.0</v>
+        <v>1002.0</v>
       </c>
       <c r="O137" s="2">
-        <v>543.0</v>
+        <v>544.0</v>
       </c>
       <c r="P137" s="2">
         <v>427.0</v>
@@ -10249,7 +10249,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>1106.0</v>
+        <v>1118.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10261,13 +10261,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>1106.0</v>
+        <v>1118.0</v>
       </c>
       <c r="O140" s="2">
-        <v>595.0</v>
+        <v>603.0</v>
       </c>
       <c r="P140" s="2">
-        <v>487.0</v>
+        <v>491.0</v>
       </c>
       <c r="Q140" s="2">
         <v>24.0</v>
@@ -10276,7 +10276,7 @@
         <v>16.0</v>
       </c>
       <c r="S140" s="2">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
       <c r="T140" s="2">
         <v>4.0</v>
@@ -10288,7 +10288,7 @@
         <v>0.0</v>
       </c>
       <c r="W140" s="2">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -10320,7 +10320,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>1113.0</v>
+        <v>1128.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10332,13 +10332,13 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>1112.0</v>
+        <v>1127.0</v>
       </c>
       <c r="O141" s="2">
-        <v>689.0</v>
+        <v>696.0</v>
       </c>
       <c r="P141" s="2">
-        <v>408.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q141" s="2">
         <v>16.0</v>
@@ -10462,7 +10462,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>1192.0</v>
+        <v>1201.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10474,25 +10474,25 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>1191.0</v>
+        <v>1200.0</v>
       </c>
       <c r="O143" s="2">
-        <v>692.0</v>
+        <v>695.0</v>
       </c>
       <c r="P143" s="2">
-        <v>499.0</v>
+        <v>505.0</v>
       </c>
       <c r="Q143" s="2">
         <v>1.0</v>
       </c>
       <c r="R143" s="2">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="S143" s="2">
         <v>0.0</v>
       </c>
       <c r="T143" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U143" s="2">
         <v>0.0</v>
@@ -10501,7 +10501,7 @@
         <v>0.0</v>
       </c>
       <c r="W143" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
@@ -10746,7 +10746,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>748.0</v>
+        <v>751.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10758,10 +10758,10 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>748.0</v>
+        <v>751.0</v>
       </c>
       <c r="O147" s="2">
-        <v>384.0</v>
+        <v>387.0</v>
       </c>
       <c r="P147" s="2">
         <v>360.0</v>
@@ -10888,7 +10888,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>880.0</v>
+        <v>904.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10900,13 +10900,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>880.0</v>
+        <v>904.0</v>
       </c>
       <c r="O149" s="2">
-        <v>530.0</v>
+        <v>545.0</v>
       </c>
       <c r="P149" s="2">
-        <v>342.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q149" s="2">
         <v>8.0</v>
@@ -11101,7 +11101,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" s="2">
-        <v>850.0</v>
+        <v>858.0</v>
       </c>
       <c r="K152" s="2">
         <v>1.0</v>
@@ -11113,25 +11113,25 @@
         <v>1.0</v>
       </c>
       <c r="N152" s="2">
-        <v>849.0</v>
+        <v>857.0</v>
       </c>
       <c r="O152" s="2">
-        <v>426.0</v>
+        <v>432.0</v>
       </c>
       <c r="P152" s="2">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
       <c r="Q152" s="2">
         <v>4.0</v>
       </c>
       <c r="R152" s="2">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="S152" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T152" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U152" s="2">
         <v>0.0</v>
@@ -11140,7 +11140,7 @@
         <v>0.0</v>
       </c>
       <c r="W152" s="2">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -11172,7 +11172,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>863.0</v>
+        <v>876.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11184,10 +11184,10 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>863.0</v>
+        <v>876.0</v>
       </c>
       <c r="O153" s="2">
-        <v>422.0</v>
+        <v>435.0</v>
       </c>
       <c r="P153" s="2">
         <v>440.0</v>
@@ -11267,7 +11267,7 @@
         <v>233.0</v>
       </c>
       <c r="R154" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="S154" s="2">
         <v>3.0</v>
@@ -11282,7 +11282,7 @@
         <v>0.0</v>
       </c>
       <c r="W154" s="2">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
@@ -11409,13 +11409,13 @@
         <v>1.0</v>
       </c>
       <c r="R156" s="2">
-        <v>9.0</v>
+        <v>28.0</v>
       </c>
       <c r="S156" s="2">
         <v>1.0</v>
       </c>
       <c r="T156" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="U156" s="2">
         <v>0.0</v>
@@ -11424,7 +11424,7 @@
         <v>0.0</v>
       </c>
       <c r="W156" s="2">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
@@ -11527,7 +11527,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>1118.0</v>
+        <v>1120.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11539,13 +11539,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>1118.0</v>
+        <v>1120.0</v>
       </c>
       <c r="O158" s="2">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="P158" s="2">
-        <v>594.0</v>
+        <v>595.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
@@ -11554,10 +11554,10 @@
         <v>52.0</v>
       </c>
       <c r="S158" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="T158" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="U158" s="2">
         <v>0.0</v>
@@ -11566,7 +11566,7 @@
         <v>0.0</v>
       </c>
       <c r="W158" s="2">
-        <v>77.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
@@ -11598,7 +11598,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>1054.0</v>
+        <v>1068.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11610,13 +11610,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>1053.0</v>
+        <v>1067.0</v>
       </c>
       <c r="O159" s="2">
-        <v>618.0</v>
+        <v>625.0</v>
       </c>
       <c r="P159" s="2">
-        <v>436.0</v>
+        <v>443.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11628,7 +11628,7 @@
         <v>15.0</v>
       </c>
       <c r="T159" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="U159" s="2">
         <v>3.0</v>
@@ -11637,7 +11637,7 @@
         <v>0.0</v>
       </c>
       <c r="W159" s="2">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
@@ -11669,7 +11669,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>1206.0</v>
+        <v>1207.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11681,25 +11681,25 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>1206.0</v>
+        <v>1207.0</v>
       </c>
       <c r="O160" s="2">
         <v>613.0</v>
       </c>
       <c r="P160" s="2">
-        <v>593.0</v>
+        <v>594.0</v>
       </c>
       <c r="Q160" s="2">
         <v>0.0</v>
       </c>
       <c r="R160" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S160" s="2">
         <v>0.0</v>
       </c>
       <c r="T160" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U160" s="2">
         <v>0.0</v>
@@ -11708,7 +11708,7 @@
         <v>0.0</v>
       </c>
       <c r="W160" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
@@ -11811,7 +11811,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>1099.0</v>
+        <v>1117.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11823,16 +11823,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>1098.0</v>
+        <v>1116.0</v>
       </c>
       <c r="O162" s="2">
-        <v>100.0</v>
+        <v>111.0</v>
       </c>
       <c r="P162" s="2">
-        <v>260.0</v>
+        <v>266.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>739.0</v>
+        <v>740.0</v>
       </c>
       <c r="R162" s="2">
         <v>28.0</v>
@@ -11841,7 +11841,7 @@
         <v>1.0</v>
       </c>
       <c r="T162" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U162" s="2">
         <v>0.0</v>
@@ -11850,7 +11850,7 @@
         <v>1.0</v>
       </c>
       <c r="W162" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
@@ -11882,7 +11882,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>948.0</v>
+        <v>983.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11894,19 +11894,19 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>948.0</v>
+        <v>983.0</v>
       </c>
       <c r="O163" s="2">
-        <v>91.0</v>
+        <v>99.0</v>
       </c>
       <c r="P163" s="2">
-        <v>459.0</v>
+        <v>483.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>398.0</v>
+        <v>401.0</v>
       </c>
       <c r="R163" s="2">
-        <v>86.0</v>
+        <v>89.0</v>
       </c>
       <c r="S163" s="2">
         <v>66.0</v>
@@ -11921,7 +11921,7 @@
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>160.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -12687,22 +12687,22 @@
         <v>0.0</v>
       </c>
       <c r="R174" s="2">
-        <v>53.0</v>
+        <v>57.0</v>
       </c>
       <c r="S174" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T174" s="2">
         <v>0.0</v>
       </c>
       <c r="U174" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V174" s="2">
         <v>0.0</v>
       </c>
       <c r="W174" s="2">
-        <v>54.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
@@ -12805,7 +12805,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>862.0</v>
+        <v>868.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12817,13 +12817,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>862.0</v>
+        <v>868.0</v>
       </c>
       <c r="O176" s="2">
-        <v>417.0</v>
+        <v>419.0</v>
       </c>
       <c r="P176" s="2">
-        <v>441.0</v>
+        <v>445.0</v>
       </c>
       <c r="Q176" s="2">
         <v>4.0</v>
@@ -12832,19 +12832,19 @@
         <v>63.0</v>
       </c>
       <c r="S176" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T176" s="2">
         <v>1.0</v>
       </c>
       <c r="U176" s="2">
-        <v>43.0</v>
+        <v>46.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>137.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12876,7 +12876,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>792.0</v>
+        <v>849.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12888,13 +12888,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>792.0</v>
+        <v>849.0</v>
       </c>
       <c r="O177" s="2">
-        <v>458.0</v>
+        <v>500.0</v>
       </c>
       <c r="P177" s="2">
-        <v>334.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -12903,7 +12903,7 @@
         <v>26.0</v>
       </c>
       <c r="S177" s="2">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
       <c r="T177" s="2">
         <v>5.0</v>
@@ -12915,7 +12915,7 @@
         <v>0.0</v>
       </c>
       <c r="W177" s="2">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
@@ -12947,7 +12947,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>730.0</v>
+        <v>747.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12959,13 +12959,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>730.0</v>
+        <v>747.0</v>
       </c>
       <c r="O178" s="2">
-        <v>363.0</v>
+        <v>373.0</v>
       </c>
       <c r="P178" s="2">
-        <v>366.0</v>
+        <v>373.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
@@ -12974,19 +12974,19 @@
         <v>20.0</v>
       </c>
       <c r="S178" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="T178" s="2">
         <v>4.0</v>
       </c>
       <c r="U178" s="2">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13018,7 +13018,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>916.0</v>
+        <v>945.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13030,19 +13030,19 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>916.0</v>
+        <v>945.0</v>
       </c>
       <c r="O179" s="2">
-        <v>568.0</v>
+        <v>583.0</v>
       </c>
       <c r="P179" s="2">
-        <v>347.0</v>
+        <v>361.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="S179" s="2">
         <v>14.0</v>
@@ -13051,13 +13051,13 @@
         <v>0.0</v>
       </c>
       <c r="U179" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="V179" s="2">
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13089,7 +13089,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>638.0</v>
+        <v>662.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13101,22 +13101,22 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>638.0</v>
+        <v>662.0</v>
       </c>
       <c r="O180" s="2">
-        <v>342.0</v>
+        <v>353.0</v>
       </c>
       <c r="P180" s="2">
-        <v>296.0</v>
+        <v>309.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
       </c>
       <c r="R180" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="S180" s="2">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="T180" s="2">
         <v>3.0</v>
@@ -13128,7 +13128,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" s="2">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -13373,22 +13373,22 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
+        <v>701.0</v>
+      </c>
+      <c r="K184" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="L184" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="M184" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N184" s="2">
         <v>700.0</v>
       </c>
-      <c r="K184" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="L184" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="M184" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="N184" s="2">
-        <v>699.0</v>
-      </c>
       <c r="O184" s="2">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
       <c r="P184" s="2">
         <v>351.0</v>
@@ -13400,7 +13400,7 @@
         <v>21.0</v>
       </c>
       <c r="S184" s="2">
-        <v>24.0</v>
+        <v>28.0</v>
       </c>
       <c r="T184" s="2">
         <v>4.0</v>
@@ -13412,7 +13412,7 @@
         <v>0.0</v>
       </c>
       <c r="W184" s="2">
-        <v>83.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
@@ -13444,7 +13444,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>945.0</v>
+        <v>950.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13456,13 +13456,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>945.0</v>
+        <v>950.0</v>
       </c>
       <c r="O185" s="2">
-        <v>512.0</v>
+        <v>514.0</v>
       </c>
       <c r="P185" s="2">
-        <v>433.0</v>
+        <v>436.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
@@ -13471,7 +13471,7 @@
         <v>19.0</v>
       </c>
       <c r="S185" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T185" s="2">
         <v>1.0</v>
@@ -13483,7 +13483,7 @@
         <v>0.0</v>
       </c>
       <c r="W185" s="2">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
@@ -13728,7 +13728,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>1201.0</v>
+        <v>1208.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13740,19 +13740,19 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>1201.0</v>
+        <v>1208.0</v>
       </c>
       <c r="O189" s="2">
-        <v>501.0</v>
+        <v>505.0</v>
       </c>
       <c r="P189" s="2">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
       <c r="Q189" s="2">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="R189" s="2">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="S189" s="2">
         <v>7.0</v>
@@ -13767,7 +13767,7 @@
         <v>0.0</v>
       </c>
       <c r="W189" s="2">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
@@ -14012,7 +14012,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>1247.0</v>
+        <v>1256.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14024,13 +14024,13 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>1247.0</v>
+        <v>1256.0</v>
       </c>
       <c r="O193" s="2">
-        <v>471.0</v>
+        <v>477.0</v>
       </c>
       <c r="P193" s="2">
-        <v>553.0</v>
+        <v>556.0</v>
       </c>
       <c r="Q193" s="2">
         <v>223.0</v>
@@ -14240,13 +14240,13 @@
         <v>1307.0</v>
       </c>
       <c r="O196" s="2">
-        <v>562.0</v>
+        <v>563.0</v>
       </c>
       <c r="P196" s="2">
         <v>546.0</v>
       </c>
       <c r="Q196" s="2">
-        <v>199.0</v>
+        <v>198.0</v>
       </c>
       <c r="R196" s="2">
         <v>38.0</v>
@@ -14580,7 +14580,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>1195.0</v>
+        <v>1197.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14592,13 +14592,13 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>1195.0</v>
+        <v>1197.0</v>
       </c>
       <c r="O201" s="2">
-        <v>634.0</v>
+        <v>635.0</v>
       </c>
       <c r="P201" s="2">
-        <v>549.0</v>
+        <v>550.0</v>
       </c>
       <c r="Q201" s="2">
         <v>12.0</v>
@@ -14651,7 +14651,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>1066.0</v>
+        <v>1075.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14663,13 +14663,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>1066.0</v>
+        <v>1075.0</v>
       </c>
       <c r="O202" s="2">
-        <v>647.0</v>
+        <v>652.0</v>
       </c>
       <c r="P202" s="2">
-        <v>419.0</v>
+        <v>423.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14678,10 +14678,10 @@
         <v>7.0</v>
       </c>
       <c r="S202" s="2">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="T202" s="2">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="U202" s="2">
         <v>12.0</v>
@@ -14690,7 +14690,7 @@
         <v>1.0</v>
       </c>
       <c r="W202" s="2">
-        <v>66.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
@@ -14722,7 +14722,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>1026.0</v>
+        <v>1032.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14734,22 +14734,22 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>1026.0</v>
+        <v>1032.0</v>
       </c>
       <c r="O203" s="2">
-        <v>614.0</v>
+        <v>618.0</v>
       </c>
       <c r="P203" s="2">
         <v>409.0</v>
       </c>
       <c r="Q203" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R203" s="2">
         <v>75.0</v>
       </c>
       <c r="S203" s="2">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="T203" s="2">
         <v>8.0</v>
@@ -14761,7 +14761,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14793,7 +14793,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>1050.0</v>
+        <v>1061.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14805,22 +14805,22 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>1050.0</v>
+        <v>1061.0</v>
       </c>
       <c r="O204" s="2">
-        <v>562.0</v>
+        <v>569.0</v>
       </c>
       <c r="P204" s="2">
-        <v>471.0</v>
+        <v>474.0</v>
       </c>
       <c r="Q204" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R204" s="2">
         <v>34.0</v>
       </c>
       <c r="S204" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="T204" s="2">
         <v>0.0</v>
@@ -14832,7 +14832,7 @@
         <v>0.0</v>
       </c>
       <c r="W204" s="2">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
@@ -15006,7 +15006,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>827.0</v>
+        <v>845.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15018,19 +15018,19 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>827.0</v>
+        <v>845.0</v>
       </c>
       <c r="O207" s="2">
-        <v>454.0</v>
+        <v>457.0</v>
       </c>
       <c r="P207" s="2">
-        <v>359.0</v>
+        <v>374.0</v>
       </c>
       <c r="Q207" s="2">
         <v>14.0</v>
       </c>
       <c r="R207" s="2">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="S207" s="2">
         <v>37.0</v>
@@ -15045,7 +15045,7 @@
         <v>0.0</v>
       </c>
       <c r="W207" s="2">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
@@ -15503,7 +15503,7 @@
         <v>1038.0</v>
       </c>
       <c r="J214" s="2">
-        <v>859.0</v>
+        <v>871.0</v>
       </c>
       <c r="K214" s="2">
         <v>1.0</v>
@@ -15515,13 +15515,13 @@
         <v>0.0</v>
       </c>
       <c r="N214" s="2">
-        <v>859.0</v>
+        <v>871.0</v>
       </c>
       <c r="O214" s="2">
-        <v>460.0</v>
+        <v>467.0</v>
       </c>
       <c r="P214" s="2">
-        <v>399.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q214" s="2">
         <v>0.0</v>
@@ -15536,13 +15536,13 @@
         <v>0.0</v>
       </c>
       <c r="U214" s="2">
-        <v>60.0</v>
+        <v>67.0</v>
       </c>
       <c r="V214" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="W214" s="2">
-        <v>122.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
@@ -15716,7 +15716,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>889.0</v>
+        <v>901.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15728,13 +15728,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>889.0</v>
+        <v>901.0</v>
       </c>
       <c r="O217" s="2">
-        <v>462.0</v>
+        <v>468.0</v>
       </c>
       <c r="P217" s="2">
-        <v>426.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q217" s="2">
         <v>1.0</v>
@@ -15746,7 +15746,7 @@
         <v>51.0</v>
       </c>
       <c r="T217" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U217" s="2">
         <v>3.0</v>
@@ -15755,7 +15755,7 @@
         <v>0.0</v>
       </c>
       <c r="W217" s="2">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
@@ -15787,7 +15787,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>981.0</v>
+        <v>983.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15799,10 +15799,10 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>980.0</v>
+        <v>982.0</v>
       </c>
       <c r="O218" s="2">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="P218" s="2">
         <v>485.0</v>
@@ -15858,7 +15858,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>1191.0</v>
+        <v>1201.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15870,13 +15870,13 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>1191.0</v>
+        <v>1201.0</v>
       </c>
       <c r="O219" s="2">
-        <v>299.0</v>
+        <v>307.0</v>
       </c>
       <c r="P219" s="2">
-        <v>509.0</v>
+        <v>511.0</v>
       </c>
       <c r="Q219" s="2">
         <v>383.0</v>
@@ -16071,7 +16071,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>1006.0</v>
+        <v>1007.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16083,7 +16083,7 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>1006.0</v>
+        <v>1007.0</v>
       </c>
       <c r="O222" s="2">
         <v>312.0</v>
@@ -16092,7 +16092,7 @@
         <v>442.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="R222" s="2">
         <v>17.0</v>
@@ -16142,7 +16142,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>1023.0</v>
+        <v>1025.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16151,7 +16151,7 @@
         <v>1.0</v>
       </c>
       <c r="M223" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N223" s="2">
         <v>1023.0</v>
@@ -16163,10 +16163,10 @@
         <v>287.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>621.0</v>
+        <v>623.0</v>
       </c>
       <c r="R223" s="2">
-        <v>74.0</v>
+        <v>73.0</v>
       </c>
       <c r="S223" s="2">
         <v>34.0</v>
@@ -16181,7 +16181,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>119.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16355,7 +16355,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>936.0</v>
+        <v>943.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16367,13 +16367,13 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>936.0</v>
+        <v>943.0</v>
       </c>
       <c r="O226" s="2">
-        <v>194.0</v>
+        <v>197.0</v>
       </c>
       <c r="P226" s="2">
-        <v>413.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q226" s="2">
         <v>329.0</v>
@@ -16497,7 +16497,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>1146.0</v>
+        <v>1188.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16509,22 +16509,22 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>1146.0</v>
+        <v>1188.0</v>
       </c>
       <c r="O228" s="2">
-        <v>363.0</v>
+        <v>396.0</v>
       </c>
       <c r="P228" s="2">
-        <v>446.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q228" s="2">
         <v>337.0</v>
       </c>
       <c r="R228" s="2">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="S228" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="T228" s="2">
         <v>0.0</v>
@@ -16536,7 +16536,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>49.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16666,7 +16666,7 @@
         <v>18.0</v>
       </c>
       <c r="S230" s="2">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="T230" s="2">
         <v>0.0</v>
@@ -16678,7 +16678,7 @@
         <v>0.0</v>
       </c>
       <c r="W230" s="2">
-        <v>19.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
@@ -16805,10 +16805,10 @@
         <v>666.0</v>
       </c>
       <c r="R232" s="2">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
       <c r="S232" s="2">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="T232" s="2">
         <v>0.0</v>
@@ -16820,7 +16820,7 @@
         <v>0.0</v>
       </c>
       <c r="W232" s="2">
-        <v>142.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
